--- a/framework-pdfs/brisk-template.xlsx
+++ b/framework-pdfs/brisk-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Martin/Documents/0 Punkfrog/10 Product Mgmt/Project Management/Risk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C15563-381F-7D4B-A2DF-188FE5F0C297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5B7482-495E-9A43-B013-3FA73085717C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13960" yWindow="-23140" windowWidth="28920" windowHeight="21880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>Management Reserve</t>
   </si>
   <si>
-    <t>BRISK Analysis™</t>
-  </si>
-  <si>
     <t>MAJOR RISK</t>
   </si>
   <si>
@@ -444,17 +441,20 @@
 The costs for pre-emptive measures are already included in the main project budget, and hopefully obviate the need to use the Contingency Reserve.</t>
   </si>
   <si>
+    <t>e.g. new or unproven technology, integration failure, low performance, limits to scale, cybersecurity vulnerability, obsolescence, component incompatibility, architectural dead-ends.</t>
+  </si>
+  <si>
+    <t>e.g. Key person dependency, loss of staff, skills gap in new technology, low team motivation, inter-team communication, overcommitment or resource overload.</t>
+  </si>
+  <si>
+    <t>Include any other areas which are relevant for the project (e.g. strategic, financial, legal, security, environmental, sustainability, governance, brand, force majeure).</t>
+  </si>
+  <si>
     <t>PF/O-26:004
-2026-03-06 version 2.0.0</t>
-  </si>
-  <si>
-    <t>e.g. new or unproven technology, integration failure, low performance, limits to scale, cybersecurity vulnerability, obsolescence, component incompatibility, architectural dead-ends.</t>
-  </si>
-  <si>
-    <t>e.g. Key person dependency, loss of staff, skills gap in new technology, low team motivation, inter-team communication, overcommitment or resource overload.</t>
-  </si>
-  <si>
-    <t>Include any other areas which are relevant for the project (e.g. strategic, financial, legal, security, environmental, sustainability, governance, brand, force majeure).</t>
+2026-04-19 version 2.0.1</t>
+  </si>
+  <si>
+    <t>BRISK Analysis</t>
   </si>
 </sst>
 </file>
@@ -1136,15 +1136,24 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1159,15 +1168,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1509,20 +1509,20 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" ht="58">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B1" s="8"/>
       <c r="D1" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="75" customFormat="1" ht="27" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="A2" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
     </row>
     <row r="3" spans="1:4" s="13" customFormat="1" ht="27">
       <c r="A3" s="11" t="s">
@@ -1532,51 +1532,51 @@
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+    </row>
+    <row r="5" spans="1:4" ht="40" customHeight="1">
+      <c r="A5" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-    </row>
-    <row r="5" spans="1:4" ht="40" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+    </row>
+    <row r="6" spans="1:4" ht="57" customHeight="1">
+      <c r="A6" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-    </row>
-    <row r="6" spans="1:4" ht="57" customHeight="1">
-      <c r="A6" s="80" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:4" s="13" customFormat="1" ht="27">
       <c r="A7" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="12"/>
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A8" s="80" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
+      <c r="A8" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
     </row>
     <row r="9" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A9" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
+      <c r="A9" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
     </row>
     <row r="10" spans="1:4" s="13" customFormat="1" ht="6" customHeight="1">
       <c r="A10" s="22"/>
@@ -1586,105 +1586,105 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" ht="18">
       <c r="A11" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="C11" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="86"/>
+      <c r="D11" s="80"/>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" ht="69" customHeight="1">
-      <c r="A12" s="81" t="str">
+      <c r="A12" s="84" t="str">
         <f>'BRISK Register'!C2</f>
         <v>MAJOR RISK</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="78"/>
+        <v>50</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" ht="53" customHeight="1">
-      <c r="A13" s="82"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="59" t="str">
         <f>'BRISK Register'!C3</f>
         <v>TECHNICAL</v>
       </c>
-      <c r="C13" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="78"/>
+      <c r="C13" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="77"/>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="82"/>
+      <c r="A14" s="85"/>
       <c r="B14" s="59" t="str">
         <f>'BRISK Register'!C8</f>
         <v>PRODUCT / REQUIREMENTS</v>
       </c>
-      <c r="C14" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="78"/>
+      <c r="C14" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="77"/>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" ht="37" customHeight="1">
-      <c r="A15" s="82"/>
+      <c r="A15" s="85"/>
       <c r="B15" s="59" t="str">
         <f>'BRISK Register'!C13</f>
         <v>PERSONNEL</v>
       </c>
-      <c r="C15" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="78"/>
+      <c r="C15" s="76" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="77"/>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" ht="52" customHeight="1">
-      <c r="A16" s="82"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="59" t="str">
         <f>'BRISK Register'!C18</f>
         <v>ADMINISTRATION / MANAGEMENT</v>
       </c>
-      <c r="C16" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="78"/>
+      <c r="C16" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="77"/>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="82"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="59" t="str">
         <f>'BRISK Register'!C23</f>
         <v>SUPPLIER / EXTERNAL</v>
       </c>
-      <c r="C17" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="78"/>
+      <c r="C17" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="77"/>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A18" s="82"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="59" t="str">
         <f>'BRISK Register'!C28</f>
         <v>OPERATIONAL / DEPLOYMENT</v>
       </c>
-      <c r="C18" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="78"/>
+      <c r="C18" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="77"/>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="37" customHeight="1">
-      <c r="A19" s="83"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="59" t="str">
         <f>'BRISK Register'!C33</f>
         <v>XXX</v>
       </c>
-      <c r="C19" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="78"/>
+      <c r="C19" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="77"/>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="120" customHeight="1">
       <c r="A20" s="71" t="str">
@@ -1692,12 +1692,12 @@
         <v>PROBABILITY</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="78"/>
+        <v>94</v>
+      </c>
+      <c r="C20" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="77"/>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="151" customHeight="1">
       <c r="A21" s="71" t="str">
@@ -1705,12 +1705,12 @@
         <v>IMPACT</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="78"/>
+        <v>73</v>
+      </c>
+      <c r="C21" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="77"/>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="71" customHeight="1">
       <c r="A22" s="71" t="str">
@@ -1718,12 +1718,12 @@
         <v>PRIORITY</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="78"/>
+        <v>47</v>
+      </c>
+      <c r="C22" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="77"/>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="70" customHeight="1">
       <c r="A23" s="72" t="str">
@@ -1732,12 +1732,12 @@
 kUSD</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="78"/>
+        <v>79</v>
+      </c>
+      <c r="C23" s="76" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="77"/>
       <c r="E23" s="61"/>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="104" customHeight="1">
@@ -1746,12 +1746,12 @@
         <v>EMV</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="78"/>
+      <c r="D24" s="77"/>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="54">
       <c r="A25" s="71" t="str">
@@ -1759,12 +1759,12 @@
         <v>PRE-EMPTIVE ACTION</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="78"/>
+        <v>83</v>
+      </c>
+      <c r="C25" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="77"/>
       <c r="E25" s="61"/>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="53" customHeight="1">
@@ -1773,28 +1773,28 @@
         <v>CONTINGENCY PLAN</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="78"/>
+        <v>96</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="77"/>
       <c r="E26" s="61"/>
     </row>
     <row r="28" spans="1:17" s="13" customFormat="1" ht="27">
       <c r="A28" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" s="12"/>
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:17" ht="42" customHeight="1">
-      <c r="A29" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
+      <c r="A29" s="78" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="78"/>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="30" spans="1:17" ht="18">
       <c r="A30" s="57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="58" t="s">
         <v>17</v>
@@ -1841,13 +1841,13 @@
         <v>19</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="74" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="152" customHeight="1">
@@ -1855,10 +1855,10 @@
         <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C32" s="74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="74"/>
     </row>
@@ -2125,6 +2125,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="C11:D11"/>
@@ -2141,14 +2149,6 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -2187,40 +2187,40 @@
     <row r="2" spans="1:11" s="9" customFormat="1" ht="86" thickBot="1">
       <c r="B2" s="55"/>
       <c r="C2" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="40" t="s">
-        <v>24</v>
-      </c>
       <c r="K2" s="40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A3" s="31"/>
       <c r="B3" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>26</v>
       </c>
       <c r="D3" s="44"/>
       <c r="E3" s="48"/>
@@ -2326,10 +2326,10 @@
     <row r="8" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A8" s="31"/>
       <c r="B8" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="50"/>
@@ -2427,10 +2427,10 @@
     <row r="13" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A13" s="31"/>
       <c r="B13" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="50"/>
@@ -2528,10 +2528,10 @@
     <row r="18" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A18" s="31"/>
       <c r="B18" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="26"/>
       <c r="E18" s="50"/>
@@ -2629,10 +2629,10 @@
     <row r="23" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A23" s="31"/>
       <c r="B23" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="50"/>
@@ -2646,7 +2646,7 @@
     <row r="24" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A24" s="32"/>
       <c r="B24" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="23"/>
       <c r="D24" s="41"/>
@@ -2667,7 +2667,7 @@
     <row r="25" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A25" s="32"/>
       <c r="B25" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="23"/>
       <c r="D25" s="41"/>
@@ -2688,7 +2688,7 @@
     <row r="26" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A26" s="32"/>
       <c r="B26" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" s="23"/>
       <c r="D26" s="41"/>
@@ -2709,7 +2709,7 @@
     <row r="27" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A27" s="32"/>
       <c r="B27" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="41"/>
@@ -2730,10 +2730,10 @@
     <row r="28" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A28" s="31"/>
       <c r="B28" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="50"/>
@@ -2747,7 +2747,7 @@
     <row r="29" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A29" s="32"/>
       <c r="B29" s="30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="41"/>
@@ -2768,7 +2768,7 @@
     <row r="30" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A30" s="32"/>
       <c r="B30" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="41"/>
@@ -2789,7 +2789,7 @@
     <row r="31" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A31" s="32"/>
       <c r="B31" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="41"/>
@@ -2810,7 +2810,7 @@
     <row r="32" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A32" s="32"/>
       <c r="B32" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="41"/>
@@ -2831,10 +2831,10 @@
     <row r="33" spans="1:11" s="9" customFormat="1" ht="18">
       <c r="A33" s="31"/>
       <c r="B33" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="50"/>
@@ -2848,7 +2848,7 @@
     <row r="34" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A34" s="32"/>
       <c r="B34" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="41"/>
@@ -2869,7 +2869,7 @@
     <row r="35" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A35" s="32"/>
       <c r="B35" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="23"/>
       <c r="D35" s="41"/>
@@ -2890,7 +2890,7 @@
     <row r="36" spans="1:11" s="10" customFormat="1" ht="18">
       <c r="A36" s="32"/>
       <c r="B36" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="23"/>
       <c r="D36" s="41"/>
@@ -2911,7 +2911,7 @@
     <row r="37" spans="1:11" s="10" customFormat="1" ht="19" thickBot="1">
       <c r="A37" s="32"/>
       <c r="B37" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="33"/>
       <c r="D37" s="51"/>
@@ -2978,26 +2978,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17">
       <c r="A1" s="87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="87"/>
       <c r="D1" s="87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:5" ht="18">
       <c r="A2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>33</v>
-      </c>
       <c r="D2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>32</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="24">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="24">
         <v>100</v>
